--- a/Cropland_Data.xlsx
+++ b/Cropland_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mihirbendre/Documents/Gazelle/Gazelle_2026/Kenya_Project/Agricentric_SOC_Modeling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E71734CA-589E-F14F-A04E-DE654043F7D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CD9C5A3-CA41-3A41-8654-D4ECCBEF5473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" activeTab="4" xr2:uid="{55781C5C-DD9E-4741-90FA-EC780B587BCA}"/>
+    <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" activeTab="2" xr2:uid="{55781C5C-DD9E-4741-90FA-EC780B587BCA}"/>
   </bookViews>
   <sheets>
     <sheet name="Eor" sheetId="3" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="41">
   <si>
     <t>Cropland</t>
   </si>
@@ -154,6 +154,15 @@
   </si>
   <si>
     <t>Area:</t>
+  </si>
+  <si>
+    <t>NPK (kg/ac)</t>
+  </si>
+  <si>
+    <t>NPK (t/ha)</t>
+  </si>
+  <si>
+    <t>Net usage</t>
   </si>
 </sst>
 </file>
@@ -912,7 +921,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35B5B873-80E5-EB47-B07D-1B182938EEB5}">
-  <dimension ref="A2:G19"/>
+  <dimension ref="A2:J19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="4" max="4" width="17" customWidth="1"/>
@@ -920,7 +929,7 @@
     <col min="7" max="7" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:10">
       <c r="B2" s="4" t="s">
         <v>2</v>
       </c>
@@ -928,7 +937,7 @@
         <v>5120</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:10">
       <c r="B4" s="4" t="s">
         <v>0</v>
       </c>
@@ -936,7 +945,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:10">
       <c r="B5" s="4" t="s">
         <v>1</v>
       </c>
@@ -944,7 +953,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:10">
       <c r="B7" s="4" t="s">
         <v>6</v>
       </c>
@@ -963,8 +972,14 @@
       <c r="G7" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="1:7">
+      <c r="I7" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="B8" t="s">
         <v>3</v>
       </c>
@@ -985,8 +1000,15 @@
         <f>F8/404.7</f>
         <v>7.4128984432913274</v>
       </c>
-    </row>
-    <row r="9" spans="1:7">
+      <c r="I8">
+        <v>75</v>
+      </c>
+      <c r="J8">
+        <f>I8*2.47105</f>
+        <v>185.32874999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="B9" t="s">
         <v>19</v>
       </c>
@@ -1008,8 +1030,15 @@
         <f>F9/404.7</f>
         <v>4.4477390659747966</v>
       </c>
-    </row>
-    <row r="10" spans="1:7">
+      <c r="I9">
+        <v>100</v>
+      </c>
+      <c r="J9">
+        <f>I9*2.47105</f>
+        <v>247.10499999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="B10" t="s">
         <v>5</v>
       </c>
@@ -1020,12 +1049,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="11" spans="1:10">
+      <c r="I11" t="s">
+        <v>40</v>
+      </c>
+      <c r="J11">
+        <f>J8*C8 +J9 * C9</f>
+        <v>195.21294999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="B13" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:10">
       <c r="B15" s="9" t="s">
         <v>25</v>
       </c>
@@ -1034,7 +1072,7 @@
       </c>
       <c r="D15" s="4"/>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:10">
       <c r="A16" s="7" t="s">
         <v>29</v>
       </c>

--- a/Cropland_Data.xlsx
+++ b/Cropland_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mihirbendre/Documents/Gazelle/Gazelle_2026/Kenya_Project/Agricentric_SOC_Modeling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CD9C5A3-CA41-3A41-8654-D4ECCBEF5473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01E10F56-6DAC-A843-B338-C5D1A7616F29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" activeTab="2" xr2:uid="{55781C5C-DD9E-4741-90FA-EC780B587BCA}"/>
+    <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" activeTab="4" xr2:uid="{55781C5C-DD9E-4741-90FA-EC780B587BCA}"/>
   </bookViews>
   <sheets>
     <sheet name="Eor" sheetId="3" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="54">
   <si>
     <t>Cropland</t>
   </si>
@@ -163,6 +163,45 @@
   </si>
   <si>
     <t>Net usage</t>
+  </si>
+  <si>
+    <t>(t/ha)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (kg/ha)</t>
+  </si>
+  <si>
+    <t>Avg (t/ha)</t>
+  </si>
+  <si>
+    <t>kg/ha</t>
+  </si>
+  <si>
+    <t>Synth Fertilizer: DAP</t>
+  </si>
+  <si>
+    <t>Synth Fertilizer: Blend, NPK</t>
+  </si>
+  <si>
+    <t>t/ha</t>
+  </si>
+  <si>
+    <t>Proportion:</t>
+  </si>
+  <si>
+    <t>Synthetic Fertilizer</t>
+  </si>
+  <si>
+    <t>Manure (t/ha) rough</t>
+  </si>
+  <si>
+    <t>Synthetic Fertilizer (CAN)</t>
+  </si>
+  <si>
+    <t>(kg/ha)</t>
+  </si>
+  <si>
+    <t>NPK (kg/ha)</t>
   </si>
 </sst>
 </file>
@@ -602,14 +641,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90554D8C-73DA-F04F-89DA-2D56E50B5786}">
-  <dimension ref="A3:G15"/>
+  <dimension ref="A3:J15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="4" max="4" width="15.83203125" customWidth="1"/>
     <col min="6" max="6" width="13.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:10">
       <c r="B3" s="4" t="s">
         <v>2</v>
       </c>
@@ -617,7 +656,7 @@
         <v>4636</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:10">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -625,7 +664,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
         <v>1</v>
       </c>
@@ -633,7 +672,12 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="7" spans="1:10">
+      <c r="I7" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="B8" s="4" t="s">
         <v>6</v>
       </c>
@@ -652,8 +696,14 @@
       <c r="G8" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="9" spans="1:7">
+      <c r="I8" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="B9" s="5" t="s">
         <v>3</v>
       </c>
@@ -674,8 +724,15 @@
         <f>F9*0.00247105</f>
         <v>2.8911284999999998</v>
       </c>
-    </row>
-    <row r="10" spans="1:7">
+      <c r="I9">
+        <v>200</v>
+      </c>
+      <c r="J9">
+        <f>I9/1000</f>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="B10" s="5" t="s">
         <v>32</v>
       </c>
@@ -686,7 +743,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:10">
       <c r="B11" s="5" t="s">
         <v>24</v>
       </c>
@@ -708,7 +765,7 @@
         <v>6.7953874999999995</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:10">
       <c r="A14" s="4" t="s">
         <v>28</v>
       </c>
@@ -716,7 +773,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>27</v>
       </c>
@@ -731,13 +788,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAF5E9CF-2D86-EC4C-AE3F-E3464696C19B}">
-  <dimension ref="A2:E18"/>
+  <dimension ref="A2:H18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5">
+    <row r="2" spans="2:8">
       <c r="B2" s="4" t="s">
         <v>2</v>
       </c>
@@ -745,7 +803,7 @@
         <v>4636</v>
       </c>
     </row>
-    <row r="4" spans="2:5">
+    <row r="4" spans="2:8">
       <c r="B4" s="4" t="s">
         <v>0</v>
       </c>
@@ -753,7 +811,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:5">
+    <row r="5" spans="2:8">
       <c r="B5" s="4" t="s">
         <v>1</v>
       </c>
@@ -761,7 +819,12 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="7" spans="2:5">
+    <row r="6" spans="2:8">
+      <c r="G6" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8">
       <c r="B7" s="4" t="s">
         <v>6</v>
       </c>
@@ -774,8 +837,14 @@
       <c r="E7" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="2:5">
+      <c r="G7" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8">
       <c r="B8" s="4" t="s">
         <v>3</v>
       </c>
@@ -789,8 +858,15 @@
         <f>D8*0.404686</f>
         <v>0.60702900000000004</v>
       </c>
-    </row>
-    <row r="9" spans="2:5">
+      <c r="G8">
+        <v>100</v>
+      </c>
+      <c r="H8">
+        <f>G8/1000</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8">
       <c r="B9" s="4" t="s">
         <v>4</v>
       </c>
@@ -804,8 +880,15 @@
         <f t="shared" ref="E9:E15" si="0">D9*0.404686</f>
         <v>20.234300000000001</v>
       </c>
-    </row>
-    <row r="10" spans="2:5">
+      <c r="G9">
+        <v>500</v>
+      </c>
+      <c r="H9">
+        <f t="shared" ref="H9:H11" si="1">G9/1000</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8">
       <c r="B10" s="4" t="s">
         <v>13</v>
       </c>
@@ -819,8 +902,15 @@
         <f t="shared" si="0"/>
         <v>0.5260918</v>
       </c>
-    </row>
-    <row r="11" spans="2:5">
+      <c r="G10">
+        <v>100</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="1"/>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8">
       <c r="B11" s="4" t="s">
         <v>14</v>
       </c>
@@ -834,8 +924,15 @@
         <f t="shared" si="0"/>
         <v>0.5260918</v>
       </c>
-    </row>
-    <row r="12" spans="2:5">
+      <c r="G11">
+        <v>100</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="1"/>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8">
       <c r="B12" t="s">
         <v>15</v>
       </c>
@@ -850,7 +947,7 @@
         <v>4.0468599999999997</v>
       </c>
     </row>
-    <row r="13" spans="2:5">
+    <row r="13" spans="2:8">
       <c r="B13" t="s">
         <v>16</v>
       </c>
@@ -865,7 +962,7 @@
         <v>2.0234299999999998</v>
       </c>
     </row>
-    <row r="14" spans="2:5">
+    <row r="14" spans="2:8">
       <c r="B14" t="s">
         <v>17</v>
       </c>
@@ -880,7 +977,7 @@
         <v>1.2140580000000001</v>
       </c>
     </row>
-    <row r="15" spans="2:5">
+    <row r="15" spans="2:8">
       <c r="B15" t="s">
         <v>18</v>
       </c>
@@ -895,18 +992,25 @@
         <v>0.80937199999999998</v>
       </c>
     </row>
-    <row r="16" spans="2:5">
+    <row r="16" spans="2:8">
       <c r="C16" s="2"/>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:8">
       <c r="A17" s="4" t="s">
         <v>28</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="18" spans="1:2">
+      <c r="G17" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H17">
+        <f>H8*C8+H9*C9+H10*C10+H11*C11</f>
+        <v>0.25000000000000006</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" t="s">
         <v>27</v>
       </c>
@@ -1004,8 +1108,8 @@
         <v>75</v>
       </c>
       <c r="J8">
-        <f>I8*2.47105</f>
-        <v>185.32874999999999</v>
+        <f>I8/404.7</f>
+        <v>0.18532246108228317</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1034,8 +1138,8 @@
         <v>100</v>
       </c>
       <c r="J9">
-        <f>I9*2.47105</f>
-        <v>247.10499999999999</v>
+        <f>I9/404.7</f>
+        <v>0.24709661477637757</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1055,7 +1159,7 @@
       </c>
       <c r="J11">
         <f>J8*C8 +J9 * C9</f>
-        <v>195.21294999999998</v>
+        <v>0.19520632567333829</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1125,10 +1229,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53518C36-D1AB-2C4E-9321-960CAD2347AA}">
-  <dimension ref="A2:B18"/>
+  <dimension ref="A2:E18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>37</v>
       </c>
@@ -1136,20 +1240,53 @@
         <v>15358</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
+    <row r="3" spans="1:5">
+      <c r="D3" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="B4" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
         <v>34</v>
       </c>
-      <c r="B3">
+      <c r="B5">
         <v>0.56999999999999995</v>
       </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
+      <c r="D5">
+        <v>100</v>
+      </c>
+      <c r="E5">
+        <f>D5/1000</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
         <v>35</v>
       </c>
-      <c r="B4">
+      <c r="B6">
         <v>0.3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="D7" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="D8" s="5">
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1175,28 +1312,55 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01B0985F-BDF1-9A4B-BE3B-FD450947079A}">
-  <dimension ref="A2:B18"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
         <v>37</v>
       </c>
-      <c r="B2">
+      <c r="B1">
         <v>9678</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B3">
-        <v>0.86450000000000005</v>
+      <c r="A3" s="4" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4">
+        <v>0.86450000000000005</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
         <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>150</v>
+      </c>
+      <c r="B9">
+        <f>A9/1000</f>
+        <v>0.15</v>
       </c>
     </row>
     <row r="17" spans="1:2">

--- a/Cropland_Data.xlsx
+++ b/Cropland_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mihirbendre/Documents/Gazelle/Gazelle_2026/Kenya_Project/Agricentric_SOC_Modeling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01E10F56-6DAC-A843-B338-C5D1A7616F29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9F00399-2BB6-F84C-9103-71273F6B46A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" activeTab="4" xr2:uid="{55781C5C-DD9E-4741-90FA-EC780B587BCA}"/>
+    <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" activeTab="1" xr2:uid="{55781C5C-DD9E-4741-90FA-EC780B587BCA}"/>
   </bookViews>
   <sheets>
     <sheet name="Eor" sheetId="3" r:id="rId1"/>

--- a/Cropland_Data.xlsx
+++ b/Cropland_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mihirbendre/Documents/Gazelle/Gazelle_2026/Kenya_Project/Agricentric_SOC_Modeling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9F00399-2BB6-F84C-9103-71273F6B46A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21BA52B4-DBF2-BE47-A8BA-E265CCCB9877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" activeTab="1" xr2:uid="{55781C5C-DD9E-4741-90FA-EC780B587BCA}"/>
+    <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" activeTab="4" xr2:uid="{55781C5C-DD9E-4741-90FA-EC780B587BCA}"/>
   </bookViews>
   <sheets>
     <sheet name="Eor" sheetId="3" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="51">
   <si>
     <t>Cropland</t>
   </si>
@@ -117,9 +117,6 @@
     <t>Potato</t>
   </si>
   <si>
-    <t>Area (unit?)</t>
-  </si>
-  <si>
     <t>All</t>
   </si>
   <si>
@@ -130,12 +127,6 @@
   </si>
   <si>
     <t>Ntu</t>
-  </si>
-  <si>
-    <t>Nth</t>
-  </si>
-  <si>
-    <t>Cmx</t>
   </si>
   <si>
     <t>Beans, etc.</t>
@@ -674,7 +665,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="I7" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -691,16 +682,16 @@
         <v>23</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>10</v>
       </c>
       <c r="I8" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J8" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -734,7 +725,7 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C10">
         <v>0.05</v>
@@ -767,7 +758,7 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>2</v>
@@ -775,10 +766,10 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -800,7 +791,7 @@
         <v>2</v>
       </c>
       <c r="C2">
-        <v>4636</v>
+        <v>4387</v>
       </c>
     </row>
     <row r="4" spans="2:8">
@@ -821,7 +812,7 @@
     </row>
     <row r="6" spans="2:8">
       <c r="G6" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="2:8">
@@ -838,10 +829,10 @@
         <v>10</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="2:8">
@@ -997,13 +988,13 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>2</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H17">
         <f>H8*C8+H9*C9+H10*C10+H11*C11</f>
@@ -1012,10 +1003,10 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1077,10 +1068,10 @@
         <v>10</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1155,7 +1146,7 @@
     </row>
     <row r="11" spans="1:10">
       <c r="I11" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="J11">
         <f>J8*C8 +J9 * C9</f>
@@ -1168,59 +1159,22 @@
       </c>
     </row>
     <row r="15" spans="1:10">
-      <c r="B15" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>2</v>
-      </c>
+      <c r="B15" s="9"/>
+      <c r="C15" s="8"/>
       <c r="D15" s="4"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16">
-        <v>9.7650000000000001E-2</v>
-      </c>
-      <c r="C16">
-        <f>B16*10000</f>
-        <v>976.5</v>
-      </c>
+      <c r="A16" s="7"/>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B17">
-        <v>3.3376999999999997E-2</v>
-      </c>
-      <c r="C17">
-        <f t="shared" ref="C17" si="0">B17*10000</f>
-        <v>333.77</v>
-      </c>
+      <c r="A17" s="7"/>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B18">
-        <v>3.7910000000000001E-3</v>
-      </c>
-      <c r="C18">
-        <f>B18*10000</f>
-        <v>37.910000000000004</v>
-      </c>
+      <c r="A18" s="7"/>
     </row>
     <row r="19" spans="1:3">
-      <c r="B19" s="6">
-        <f>SUM(B16:B18)</f>
-        <v>0.13481799999999999</v>
-      </c>
-      <c r="C19" s="6">
-        <f>B19*10000</f>
-        <v>1348.1799999999998</v>
-      </c>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1234,7 +1188,7 @@
   <sheetData>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B2" s="11">
         <v>15358</v>
@@ -1242,23 +1196,23 @@
     </row>
     <row r="3" spans="1:5">
       <c r="D3" s="4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="B4" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B5">
         <v>0.56999999999999995</v>
@@ -1273,7 +1227,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B6">
         <v>0.3</v>
@@ -1281,7 +1235,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="D7" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1291,7 +1245,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>2</v>
@@ -1299,10 +1253,10 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1317,7 +1271,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B1">
         <v>9678</v>
@@ -1325,12 +1279,12 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B4">
         <v>0.86450000000000005</v>
@@ -1338,20 +1292,20 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1365,7 +1319,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>2</v>
@@ -1373,10 +1327,10 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/Cropland_Data.xlsx
+++ b/Cropland_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mihirbendre/Documents/Gazelle/Gazelle_2026/Kenya_Project/Agricentric_SOC_Modeling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21BA52B4-DBF2-BE47-A8BA-E265CCCB9877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F77BF92-C2F5-214D-A615-7D0C4378CFF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" activeTab="4" xr2:uid="{55781C5C-DD9E-4741-90FA-EC780B587BCA}"/>
   </bookViews>
@@ -739,7 +739,7 @@
         <v>24</v>
       </c>
       <c r="C11">
-        <v>0.6</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="D11">
         <v>25</v>

--- a/Cropland_Data.xlsx
+++ b/Cropland_Data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mihirbendre/Documents/Gazelle/Gazelle_2026/Kenya_Project/Agricentric_SOC_Modeling/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mihirbendre/Documents/Gazelle/Gazelle_2026/Kenya_Project/ER_&amp;_Proj_Docs_Agricentric/Agricentric_SOC_Modeling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F77BF92-C2F5-214D-A615-7D0C4378CFF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5477A26B-8862-4044-BDE0-B9E340355ABC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" activeTab="4" xr2:uid="{55781C5C-DD9E-4741-90FA-EC780B587BCA}"/>
+    <workbookView xWindow="5560" yWindow="2180" windowWidth="29400" windowHeight="18400" activeTab="4" xr2:uid="{55781C5C-DD9E-4741-90FA-EC780B587BCA}"/>
   </bookViews>
   <sheets>
     <sheet name="Eor" sheetId="3" r:id="rId1"/>
@@ -644,7 +644,7 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>4636</v>
+        <v>4387</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -791,7 +791,7 @@
         <v>2</v>
       </c>
       <c r="C2">
-        <v>4387</v>
+        <v>4636</v>
       </c>
     </row>
     <row r="4" spans="2:8">
